--- a/Piaui/2026/ResultadosTRI_3EM_MT/Simulado_I/ResumoTheta_3EM_MT_S1.xlsx
+++ b/Piaui/2026/ResultadosTRI_3EM_MT/Simulado_I/ResumoTheta_3EM_MT_S1.xlsx
@@ -389,7 +389,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>280.37932125949</v>
+        <v>289.789093260083</v>
       </c>
     </row>
     <row r="3">
@@ -397,7 +397,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>60.4140166233068</v>
+        <v>66.2240549839657</v>
       </c>
     </row>
     <row r="4">
@@ -405,7 +405,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>21.5472440520654</v>
+        <v>22.8525008443055</v>
       </c>
     </row>
     <row r="5">
@@ -413,7 +413,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>191.758242967625</v>
+        <v>196.840972356023</v>
       </c>
     </row>
     <row r="6">
@@ -421,7 +421,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>232.532652771379</v>
+        <v>236.55363547892</v>
       </c>
     </row>
     <row r="7">
@@ -429,7 +429,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>265.72436718563</v>
+        <v>273.114361431317</v>
       </c>
     </row>
     <row r="8">
@@ -437,7 +437,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>323.138048997823</v>
+        <v>337.239478346614</v>
       </c>
     </row>
     <row r="9">
@@ -445,7 +445,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>475.283564078263</v>
+        <v>496.290612892676</v>
       </c>
     </row>
     <row r="10">
@@ -453,7 +453,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>0.655057148454495</v>
+        <v>0.691433597756571</v>
       </c>
     </row>
     <row r="11">
@@ -461,7 +461,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="n">
-        <v>2.46557297944758</v>
+        <v>2.51048460705325</v>
       </c>
     </row>
   </sheetData>

--- a/Piaui/2026/ResultadosTRI_3EM_MT/Simulado_I/ResumoTheta_3EM_MT_S1.xlsx
+++ b/Piaui/2026/ResultadosTRI_3EM_MT/Simulado_I/ResumoTheta_3EM_MT_S1.xlsx
@@ -389,7 +389,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>289.789093260083</v>
+        <v>280.37932125949</v>
       </c>
     </row>
     <row r="3">
@@ -397,7 +397,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>66.2240549839657</v>
+        <v>60.4140166233068</v>
       </c>
     </row>
     <row r="4">
@@ -405,7 +405,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>22.8525008443055</v>
+        <v>21.5472440520654</v>
       </c>
     </row>
     <row r="5">
@@ -413,7 +413,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>196.840972356023</v>
+        <v>191.758242967625</v>
       </c>
     </row>
     <row r="6">
@@ -421,7 +421,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>236.55363547892</v>
+        <v>232.532652771379</v>
       </c>
     </row>
     <row r="7">
@@ -429,7 +429,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>273.114361431317</v>
+        <v>265.72436718563</v>
       </c>
     </row>
     <row r="8">
@@ -437,7 +437,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>337.239478346614</v>
+        <v>323.138048997823</v>
       </c>
     </row>
     <row r="9">
@@ -445,7 +445,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>496.290612892676</v>
+        <v>475.283564078263</v>
       </c>
     </row>
     <row r="10">
@@ -453,7 +453,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>0.691433597756571</v>
+        <v>0.655057148454495</v>
       </c>
     </row>
     <row r="11">
@@ -461,7 +461,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="n">
-        <v>2.51048460705325</v>
+        <v>2.46557297944758</v>
       </c>
     </row>
   </sheetData>
